--- a/33張test裁切結果_yolo26.xlsx
+++ b/33張test裁切結果_yolo26.xlsx
@@ -463,7 +463,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -477,12 +477,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>176,51,269,288</t>
+          <t>173,40,272,294</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53,137,180,397</t>
+          <t>54,127,183,400</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.764</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>112,64,247,388</t>
+          <t>128,61,242,386</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.745</v>
+        <v>0.841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>210,126,300,365</t>
+          <t>208,130,293,368</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -595,7 +595,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.745</v>
+        <v>0.862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>113,99,242,380</t>
+          <t>124,104,236,374</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.767</v>
+        <v>0.844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>137,57,271,381</t>
+          <t>146,56,272,361</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.752</v>
+        <v>0.825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102,64,229,370</t>
+          <t>112,40,221,377</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.726</v>
+        <v>0.796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>142,92,237,343</t>
+          <t>146,94,233,341</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -727,7 +727,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.696</v>
+        <v>0.76</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -741,12 +741,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>162,126,281,394</t>
+          <t>168,123,275,385</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
     </row>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.746</v>
+        <v>0.84</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102,78,175,273</t>
+          <t>96,80,174,274</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -793,7 +793,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -807,12 +807,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>130,85,249,386</t>
+          <t>128,75,251,385</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -840,12 +840,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>212,99,322,357</t>
+          <t>213,91,326,362</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.759</v>
+        <v>0.847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>106,87,231,375</t>
+          <t>116,77,225,372</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.642</v>
+        <v>0.704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>137,3,240,261</t>
+          <t>143,0,238,254</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.711</v>
+        <v>0.782</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>156,35,249,297</t>
+          <t>160,34,242,304</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.774</v>
+        <v>0.804</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>179,71,263,305</t>
+          <t>179,70,260,308</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69,69,209,385</t>
+          <t>82,73,206,386</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1024,7 +1024,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.695</v>
+        <v>0.801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>140,92,264,394</t>
+          <t>152,100,261,398</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1057,7 +1057,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.717</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>181,89,311,394</t>
+          <t>192,70,309,394</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.769</v>
+        <v>0.785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>98,148,207,371</t>
+          <t>96,149,204,374</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>0.783</v>
+        <v>0.902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>146,136,262,400</t>
+          <t>155,129,254,398</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1156,7 +1156,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.742</v>
+        <v>0.858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>88,96,217,399</t>
+          <t>101,95,212,400</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.77</v>
+        <v>0.899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>110,141,252,390</t>
+          <t>121,133,241,387</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.748</v>
+        <v>0.796</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>215,126,334,369</t>
+          <t>218,120,330,368</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1255,7 +1255,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>0.747</v>
+        <v>0.889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>92,77,199,346</t>
+          <t>83,78,190,344</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>0.772</v>
+        <v>0.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>152,75,289,361</t>
+          <t>162,69,291,354</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0.717</v>
+        <v>0.838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>92,113,218,377</t>
+          <t>99,108,208,377</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.734</v>
+        <v>0.83</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>172,117,304,400</t>
+          <t>185,105,302,400</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.836</v>
+        <v>0.828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>112,144,211,364</t>
+          <t>113,133,212,365</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.918</v>
+        <v>0.928</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>143,73,261,370</t>
+          <t>146,61,263,363</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0.713</v>
+        <v>0.827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>167,104,303,400</t>
+          <t>180,107,299,400</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1486,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>0.759</v>
+        <v>0.784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74,123,204,400</t>
+          <t>84,109,204,400</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>0.786</v>
+        <v>0.779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>130,96,261,373</t>
+          <t>141,92,251,365</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
     </row>
